--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -43,9 +43,6 @@
     <t xml:space="preserve">int</t>
   </si>
   <si>
-    <t xml:space="preserve">List&lt;string&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Id</t>
   </si>
   <si>
@@ -55,32 +52,13 @@
     <t xml:space="preserve">GateHp</t>
   </si>
   <si>
-    <t xml:space="preserve">WaveIds</t>
+    <t xml:space="preserve">Wave_List</t>
   </si>
   <si>
     <t xml:space="preserve">Stage_01</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">[“Wave_01_01”, “Wave_01_02”, “Wave_01_03”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="&quot;맑은 고딕&quot;"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
+    <t xml:space="preserve">Wave_01_01,Wave_01_02,Wave_01_03</t>
   </si>
 </sst>
 </file>
@@ -90,7 +68,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -149,8 +127,8 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="129"/>
     </font>
     <font>
@@ -166,13 +144,6 @@
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -268,11 +239,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -288,11 +259,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -598,8 +569,8 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -609,17 +580,17 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" s="10" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
@@ -629,7 +600,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>120</v>
@@ -638,7 +609,7 @@
         <v>100</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>

--- a/JsonConverter/ExcelFiles/StageData.xlsx
+++ b/JsonConverter/ExcelFiles/StageData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -58,7 +58,61 @@
     <t xml:space="preserve">Stage_01</t>
   </si>
   <si>
-    <t xml:space="preserve">Wave_01_01,Wave_01_02,Wave_01_03</t>
+    <t xml:space="preserve">Wave_01_01,Wave_01_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_02_01,Wave_02_02,Wave_02_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_03_01,Wave_03_02,Wave_03_03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_04_01,Wave_04_02,Wave_04_03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_05_01,Wave_05_02,Wave_05_03,Wave_05_04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_06_01,Wave_06_02,Wave_06_03,Wave_06_04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_07_01,Wave_07_02,Wave_07_03,Wave_07_04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_08_01,Wave_08_02,Wave_08_03,Wave_08_04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_09_01,Wave_09_02,Wave_09_03,Wave_09_04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave_10_01,Wave_10_02,Wave_10_03,Wave_10_04 </t>
   </si>
 </sst>
 </file>
@@ -628,10 +682,18 @@
       <c r="S4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -649,10 +711,18 @@
       <c r="S5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -670,10 +740,18 @@
       <c r="S6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -691,10 +769,18 @@
       <c r="S7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -712,10 +798,18 @@
       <c r="S8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -733,10 +827,18 @@
       <c r="S9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -754,10 +856,18 @@
       <c r="S10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -775,10 +885,18 @@
       <c r="S11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -796,10 +914,18 @@
       <c r="S12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
